--- a/layout/CATALOGOS/PAG_VENA_V1.xlsx
+++ b/layout/CATALOGOS/PAG_VENA_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\CATALOGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A08F1C3-9926-42CE-8550-C459E31AC612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{625C4F65-C34A-4524-8CDC-B9BA661AF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="4970" windowWidth="21900" windowHeight="15950" xr2:uid="{28B0C1E9-8CB4-4304-A5A6-EB886CCE75B0}"/>
+    <workbookView xWindow="620" yWindow="7640" windowWidth="24380" windowHeight="13710" xr2:uid="{8CA95100-5013-4A54-9D47-933B7A8D6B71}"/>
   </bookViews>
   <sheets>
     <sheet name="PAG_VENA_V1" sheetId="1" r:id="rId1"/>
@@ -94,18 +94,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -129,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -138,12 +132,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -479,11 +467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926E1760-789F-42C7-B3F3-EC611A7073B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BCCDDF-78AA-438F-9042-A05C902AB612}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="32.08984375" customWidth="1"/>
+    <col min="3" max="3" width="121" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -522,13 +510,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
